--- a/caderno_c3/PSH_Controle_Referencias_Normativas_MOP_Atividade_3.2.2.xlsx
+++ b/caderno_c3/PSH_Controle_Referencias_Normativas_MOP_Atividade_3.2.2.xlsx
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="L5" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M5" s="38" t="n"/>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="F6" s="38" t="inlineStr">
         <is>
-          <t>O Acordo de Empréstimo, item (j)(vii), pede a identificação das áreas rurais da Parte 3.2. O mapa most…</t>
+          <t>O Acordo de Empréstimo, item (j)(vii) das definições, exige a identificação das áreas rurais da Parte…</t>
         </is>
       </c>
       <c r="G6" s="38" t="inlineStr">
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="L6" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M6" s="38" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D7" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo</t>
         </is>
       </c>
       <c r="E7" s="38" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="F7" s="38" t="inlineStr">
         <is>
-          <t>…se sujeita ao Marco Regulatório das Organizações da Sociedade Civil (MROSC), e o uso da infraestrutura pública é formalizado por Acordo de Cooperação, depois que o munic…</t>
+          <t>…submete-se ao Marco Regulatório das Organizações da Sociedade Civil (MROSC), e o uso da infraestrutura pública é formalizado por Acordo de Cooperação, após a aprovação d…</t>
         </is>
       </c>
       <c r="G7" s="38" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="L7" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M7" s="38" t="n"/>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="D8" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo › Quadro “Alternativas de modelo de gestão e seu amparo legal”, linha “Amparo legal”</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo › Quadro “Alternativas de modelo de gestão e respectivo amparo legal”, linha “Amparo legal”</t>
         </is>
       </c>
       <c r="E8" s="38" t="inlineStr">
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="L8" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M8" s="38" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="D9" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo › Quadro “Alternativas de modelo de gestão e seu amparo legal”, linha “Amparo legal”</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo › Quadro “Alternativas de modelo de gestão e respectivo amparo legal”, linha “Amparo legal”</t>
         </is>
       </c>
       <c r="E9" s="38" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="F9" s="38" t="inlineStr">
         <is>
-          <t>MROSC; a nota técnica cita também o Decreto nº 11.599/2023 e a Portaria Funasa nº 2.777/2025</t>
+          <t>MROSC; a nota técnica cita também o Decreto nº 11.599/2023 e a Portaria nº 2.777/2025 da Fundação Nacional de Saúde (Funasa)</t>
         </is>
       </c>
       <c r="G9" s="38" t="inlineStr">
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="L9" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M9" s="38" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D10" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo › Quadro “Alternativas de modelo de gestão e seu amparo legal”, linha “Amparo legal”</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo › Quadro “Alternativas de modelo de gestão e respectivo amparo legal”, linha “Amparo legal”</t>
         </is>
       </c>
       <c r="E10" s="38" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F10" s="38" t="inlineStr">
         <is>
-          <t>MROSC; a nota técnica cita também o Decreto nº 11.599/2023 e a Portaria Funasa nº 2.777/2025</t>
+          <t>MROSC; a nota técnica cita também o Decreto nº 11.599/2023 e a Portaria nº 2.777/2025 da Fundação Nacional de Saúde (Funasa)</t>
         </is>
       </c>
       <c r="G10" s="38" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="L10" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M10" s="38" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="D11" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo › Quadro “Alternativas de modelo de gestão e seu amparo legal”, linha “Amparo legal”</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo › Quadro “Alternativas de modelo de gestão e respectivo amparo legal”, linha “Amparo legal”</t>
         </is>
       </c>
       <c r="E11" s="38" t="inlineStr">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="L11" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M11" s="38" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D12" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo › Quadro “Alternativas de modelo de gestão e seu amparo legal”, linha “Amparo legal”</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo › Quadro “Alternativas de modelo de gestão e respectivo amparo legal”, linha “Amparo legal”</t>
         </is>
       </c>
       <c r="E12" s="38" t="inlineStr">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="L12" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M12" s="38" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="D13" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo</t>
         </is>
       </c>
       <c r="E13" s="38" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="F13" s="38" t="inlineStr">
         <is>
-          <t>…restam o serviço de forma associada, por meio de um consórcio público (BRASIL, 2005). É a alternativa preliminar apontada para o Paraná, porque muitos municípios já integ…</t>
+          <t>…s prestam o serviço de forma associada, por meio de consórcio público (BRASIL, 2005). Esta é a alternativa preliminarmente indicada para o Paraná, em razão da participaçã…</t>
         </is>
       </c>
       <c r="G13" s="38" t="inlineStr">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="L13" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M13" s="38" t="n"/>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D14" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo</t>
         </is>
       </c>
       <c r="E14" s="38" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="L14" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M14" s="38" t="n"/>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="D15" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo</t>
         </is>
       </c>
       <c r="E15" s="38" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="F15" s="38" t="inlineStr">
         <is>
-          <t>…de um mandato para outro. A nota técnica do Componente 3 cita ainda o Decreto nº 11.599/2023 e a Portaria Funasa nº 2.777/2025 como respaldo aos arranjos associativos no…</t>
+          <t>…à gestão entre mandatos. A nota técnica do componente cita, ainda, o Decreto nº 11.599/2023 e a Portaria Funasa nº 2.777/2025 como fundamento dos arranjos associativos n…</t>
         </is>
       </c>
       <c r="G15" s="38" t="inlineStr">
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="L15" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M15" s="38" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D16" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo</t>
         </is>
       </c>
       <c r="E16" s="38" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="F16" s="38" t="inlineStr">
         <is>
-          <t>…nota técnica do Componente 3 cita ainda o Decreto nº 11.599/2023 e a Portaria Funasa nº 2.777/2025 como respaldo aos arranjos associativos no marco legal do saneamento a…</t>
+          <t>…nota técnica do componente cita, ainda, o Decreto nº 11.599/2023 e a Portaria Funasa nº 2.777/2025 como fundamento dos arranjos associativos no marco legal do saneamento…</t>
         </is>
       </c>
       <c r="G16" s="38" t="inlineStr">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="L16" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M16" s="38" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D17" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo</t>
         </is>
       </c>
       <c r="E17" s="38" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="F17" s="38" t="inlineStr">
         <is>
-          <t>Conferir o amparo citado pela nota técnica. O Decreto nº 11.599/2023 trata da prestação regionalizada e do apoio técnico e financeiro da União; a…</t>
+          <t>Conferir o fundamento legal citado pela nota técnica. O Decreto nº 11.599/2023 trata da prestação regionalizada e do apoio técnico e financeiro da União; a…</t>
         </is>
       </c>
       <c r="G17" s="38" t="inlineStr">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="L17" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M17" s="38" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D18" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo</t>
         </is>
       </c>
       <c r="E18" s="38" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="F18" s="38" t="inlineStr">
         <is>
-          <t>…a prestação regionalizada e do apoio técnico e financeiro da União; a Portaria Funasa nº 2.777/2025 aparece no portal da Funasa como seleção de propostas de abastecimento…</t>
+          <t>…a prestação regionalizada e do apoio técnico e financeiro da União; a Portaria Funasa nº 2.777/2025 consta no portal da Funasa como seleção de propostas de abastecimento…</t>
         </is>
       </c>
       <c r="G18" s="38" t="inlineStr">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="L18" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M18" s="38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="D19" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo</t>
         </is>
       </c>
       <c r="E19" s="38" t="inlineStr">
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="L19" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M19" s="38" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="D20" s="38" t="inlineStr">
         <is>
-          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e escolha do modelo</t>
+          <t>4. Processo de execução operacional › 4.1 Etapa 1: Estudos preliminares e definição do modelo</t>
         </is>
       </c>
       <c r="E20" s="38" t="inlineStr">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="L20" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M20" s="38" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="51" customHeight="1">
       <c r="A21" s="38" t="inlineStr">
         <is>
           <t>C-017</t>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F21" s="38" t="inlineStr">
         <is>
-          <t>…e na sustentabilidade financeira das associações. O Quadro indica as NAS aplicáveis e as medidas.</t>
+          <t>…e na sustentabilidade financeira das associações. O Quadro indica as NAS aplicáveis e as respectivas medidas.</t>
         </is>
       </c>
       <c r="G21" s="38" t="inlineStr">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="L21" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M21" s="38" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="96" customHeight="1">
+    <row r="22" ht="111" customHeight="1">
       <c r="A22" s="38" t="inlineStr">
         <is>
           <t>C-018</t>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="D22" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.1”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à implantação dos modelos de gestão”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
         </is>
       </c>
       <c r="E22" s="38" t="inlineStr">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="L22" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M22" s="38" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="L23" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M23" s="38" t="n"/>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L24" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M24" s="38" t="n"/>
     </row>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="L25" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M25" s="38" t="n"/>
     </row>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="L26" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M26" s="38" t="n"/>
     </row>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="L27" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M27" s="38" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="L28" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M28" s="38" t="n"/>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="F29" s="38" t="inlineStr">
         <is>
-          <t>…lias, os sistemas rurais costumam ser subutilizados ou abandonados. O Programa Nacional de Saneamento Rural trata a educação e a participação social como um dos três eixo…</t>
+          <t>…iada à subutilização e ao abandono de sistemas de saneamento rural. O Programa Nacional de Saneamento Rural estabelece a educação e a participação social como um dos três…</t>
         </is>
       </c>
       <c r="G29" s="38" t="inlineStr">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="L29" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M29" s="38" t="n"/>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F30" s="38" t="inlineStr">
         <is>
-          <t>…omiciliar georreferenciado. Os dados pessoais são tratados conforme a Lei Geral de Proteção de Dados Pessoais, apenas para as finalidades da ação (BRASIL, 2018).</t>
+          <t>…omiciliar georreferenciado. O tratamento dos dados pessoais observa a Lei Geral de Proteção de Dados Pessoais (LGPD) e restringe-se às finalidades da ação (BRASIL, 2018).</t>
         </is>
       </c>
       <c r="G30" s="38" t="inlineStr">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="L30" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M30" s="38" t="n"/>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="D31" s="38" t="inlineStr">
         <is>
-          <t>6. Metas, indicadores e comprovação › Quadro “Critérios de aceite e evidências da Ação 3.2.2.2”, linha “Cadastro domiciliar”</t>
+          <t>6. Metas, indicadores e comprovação › Quadro “Critérios de aceite e evidências do trabalho técnico-social”, linha “Cadastro domiciliar”</t>
         </is>
       </c>
       <c r="E31" s="38" t="inlineStr">
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="L31" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M31" s="38" t="inlineStr">
         <is>
@@ -5907,11 +5907,11 @@
         </is>
       </c>
       <c r="L32" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M32" s="38" t="n"/>
     </row>
-    <row r="33" ht="96" customHeight="1">
+    <row r="33" ht="111" customHeight="1">
       <c r="A33" s="38" t="inlineStr">
         <is>
           <t>C-029</t>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="D33" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.2”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais ao trabalho técnico-social”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
         </is>
       </c>
       <c r="E33" s="38" t="inlineStr">
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="L33" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M33" s="38" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="D34" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.2”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais ao trabalho técnico-social”</t>
         </is>
       </c>
       <c r="E34" s="38" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="F34" s="38" t="inlineStr">
         <is>
-          <t>Nota: o cadastro domiciliar segue a Lei Geral de Proteção de Dados Pessoais (BRASIL, 2018).</t>
+          <t>Nota: o cadastro domiciliar observa a Lei Geral de Proteção de Dados Pessoais (BRASIL, 2018).</t>
         </is>
       </c>
       <c r="G34" s="38" t="inlineStr">
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="L34" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M34" s="38" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="L35" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M35" s="38" t="n"/>
     </row>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="L36" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M36" s="38" t="n"/>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F37" s="38" t="inlineStr">
         <is>
-          <t>O Acordo de Empréstimo, item (j)(vii), pede a identificação das áreas rurais da Parte 3.2. Anexar a li…</t>
+          <t>O Acordo de Empréstimo, item (j)(vii) das definições, exige a identificação das áreas rurais da Parte…</t>
         </is>
       </c>
       <c r="G37" s="38" t="inlineStr">
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="L37" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M37" s="38" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="L38" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M38" s="38" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="L39" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M39" s="38" t="inlineStr">
         <is>
@@ -6415,11 +6415,11 @@
         </is>
       </c>
       <c r="L40" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M40" s="38" t="n"/>
     </row>
-    <row r="41" ht="96" customHeight="1">
+    <row r="41" ht="111" customHeight="1">
       <c r="A41" s="38" t="inlineStr">
         <is>
           <t>C-037</t>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D41" s="38" t="inlineStr">
         <is>
-          <t>6. Metas, indicadores e comprovação › Quadro “Indicadores da Ação 3.2.2.3”, linha “Análises de entrega conformes ao padrão de potabilidade”</t>
+          <t>6. Metas, indicadores e comprovação › Quadro “Indicadores da implantação dos sistemas coletivos de abastecimento de água”, linha “Análises de entrega conformes ao padrão de potabilidade”</t>
         </is>
       </c>
       <c r="E41" s="38" t="inlineStr">
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="L41" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M41" s="38" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="36" customHeight="1">
+    <row r="42" ht="51" customHeight="1">
       <c r="A42" s="38" t="inlineStr">
         <is>
           <t>C-038</t>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="F42" s="38" t="inlineStr">
         <is>
-          <t>…uso da água e a exclusão de famílias vulneráveis. O Quadro indica as NAS aplicáveis e as medidas.</t>
+          <t>…uso da água e a exclusão de famílias vulneráveis. O Quadro indica as NAS aplicáveis e as respectivas medidas.</t>
         </is>
       </c>
       <c r="G42" s="38" t="inlineStr">
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="L42" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M42" s="38" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="96" customHeight="1">
+    <row r="43" ht="126" customHeight="1">
       <c r="A43" s="38" t="inlineStr">
         <is>
           <t>C-039</t>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D43" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.3”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à implantação dos sistemas coletivos de abastecimento de água”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
         </is>
       </c>
       <c r="E43" s="38" t="inlineStr">
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="L43" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M43" s="38" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L44" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M44" s="38" t="n"/>
     </row>
@@ -6732,11 +6732,11 @@
         </is>
       </c>
       <c r="L45" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M45" s="38" t="n"/>
     </row>
-    <row r="46" ht="36" customHeight="1">
+    <row r="46" ht="51" customHeight="1">
       <c r="A46" s="38" t="inlineStr">
         <is>
           <t>C-042</t>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F46" s="38" t="inlineStr">
         <is>
-          <t>ABNT NBR 12212:2017 e NBR 12244:2006 (projeto e construção de poço tubular) e demais normas ABNT de proje…</t>
+          <t>Normas da Associação Brasileira de Normas Técnicas (ABNT) NBR 12212:2017 e NBR 12244:2006 (projeto e construção de poço tubular) e demais normas ABNT de proje…</t>
         </is>
       </c>
       <c r="G46" s="38" t="inlineStr">
@@ -6793,11 +6793,11 @@
         </is>
       </c>
       <c r="L46" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M46" s="38" t="n"/>
     </row>
-    <row r="47" ht="51" customHeight="1">
+    <row r="47" ht="66" customHeight="1">
       <c r="A47" s="38" t="inlineStr">
         <is>
           <t>C-043</t>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="F47" s="38" t="inlineStr">
         <is>
-          <t>ABNT NBR 12212:2017 e NBR 12244:2006 (projeto e construção de poço tubular) e demais normas ABNT de projeto de sistemas de…</t>
+          <t>…s da Associação Brasileira de Normas Técnicas (ABNT) NBR 12212:2017 e NBR 12244:2006 (projeto e construção de poço tubular) e demais normas ABNT de projeto de sistemas de…</t>
         </is>
       </c>
       <c r="G47" s="38" t="inlineStr">
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="L47" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M47" s="38" t="n"/>
     </row>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="L48" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M48" s="38" t="n"/>
     </row>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="L49" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M49" s="38" t="n"/>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="F50" s="38" t="inlineStr">
         <is>
-          <t>O Acordo de Empréstimo, item (j)(vii), pede a identificação das áreas rurais da Parte 3.2. Solicitar à…</t>
+          <t>O Acordo de Empréstimo, item (j)(vii) das definições, exige a identificação das áreas rurais da Parte…</t>
         </is>
       </c>
       <c r="G50" s="38" t="inlineStr">
@@ -7037,7 +7037,7 @@
         </is>
       </c>
       <c r="L50" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M50" s="38" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="F51" s="38" t="inlineStr">
         <is>
-          <t>As aquisições da Sanepar seguem o seu Regulamento de Licitações e Contratos, e as obras contratadas pelos municípios, a legislação de lici…</t>
+          <t>As aquisições da Sanepar observam o Regulamento de Licitações e Contratos da companhia, e as obras contratadas pelos municípios, a legis…</t>
         </is>
       </c>
       <c r="G51" s="38" t="inlineStr">
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="L51" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M51" s="38" t="n"/>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="D52" s="38" t="inlineStr">
         <is>
-          <t>6. Metas, indicadores e comprovação › Quadro “Critérios de aceite e evidências da Ação 3.2.2.4”, linha “Sistema implantado”</t>
+          <t>6. Metas, indicadores e comprovação › Quadro “Critérios de aceite e evidências do Programa Sanepar Rural”, linha “Sistema implantado”</t>
         </is>
       </c>
       <c r="E52" s="38" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="F52" s="38" t="inlineStr">
         <is>
-          <t>Obra concluída e em operação, com água dentro do padrão de potabilidade</t>
+          <t>Obra concluída e em operação, com água conforme o padrão de potabilidade</t>
         </is>
       </c>
       <c r="G52" s="38" t="inlineStr">
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="L52" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M52" s="38" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="96" customHeight="1">
+    <row r="53" ht="111" customHeight="1">
       <c r="A53" s="38" t="inlineStr">
         <is>
           <t>C-049</t>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="D53" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.4”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais ao Programa Sanepar Rural”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
         </is>
       </c>
       <c r="E53" s="38" t="inlineStr">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="L53" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M53" s="38" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="L54" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M54" s="38" t="n"/>
     </row>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="L55" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M55" s="38" t="n"/>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="F56" s="38" t="inlineStr">
         <is>
-          <t>As soluções seguem a ABNT NBR 17076:2024, que substituiu as normas NBR 7229 e NBR 13969 e define alternativas de tratamento lo…</t>
+          <t>As soluções observam a ABNT NBR 17076:2024, que substituiu as normas ABNT NBR 7229:1993 e NBR 13969:1997 e estabelece alternativ…</t>
         </is>
       </c>
       <c r="G56" s="38" t="inlineStr">
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="L56" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M56" s="38" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F57" s="38" t="inlineStr">
         <is>
-          <t>As soluções seguem a ABNT NBR 17076:2024, que substituiu as normas NBR 7229 e NBR 13969 e define alternativas de tratamento local para vazões de até 12.000 L/dia e car…</t>
+          <t>…oluções observam a ABNT NBR 17076:2024, que substituiu as normas ABNT NBR 7229:1993 e NBR 13969:1997 e estabelece alternativas de tratamento local para vazões de até 12.0…</t>
         </is>
       </c>
       <c r="G57" s="38" t="inlineStr">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="L57" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M57" s="38" t="n"/>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="F58" s="38" t="inlineStr">
         <is>
-          <t>…ões seguem a ABNT NBR 17076:2024, que substituiu as normas NBR 7229 e NBR 13969 e define alternativas de tratamento local para vazões de até 12.000 L/dia e carga orgânica…</t>
+          <t>…a ABNT NBR 17076:2024, que substituiu as normas ABNT NBR 7229:1993 e NBR 13969:1997 e estabelece alternativas de tratamento local para vazões de até 12.000 L/dia e carga…</t>
         </is>
       </c>
       <c r="G58" s="38" t="inlineStr">
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="L58" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M58" s="38" t="n"/>
     </row>
@@ -7602,11 +7602,11 @@
         </is>
       </c>
       <c r="L59" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M59" s="38" t="n"/>
     </row>
-    <row r="60" ht="81" customHeight="1">
+    <row r="60" ht="96" customHeight="1">
       <c r="A60" s="38" t="inlineStr">
         <is>
           <t>C-056</t>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D60" s="38" t="inlineStr">
         <is>
-          <t>6. Metas, indicadores e comprovação › Quadro “Critérios de aceite e evidências da Ação 3.2.2.5”, linha “Projeto individual”</t>
+          <t>6. Metas, indicadores e comprovação › Quadro “Critérios de aceite e evidências do esgotamento sanitário nas comunidades”, linha “Projeto individual”</t>
         </is>
       </c>
       <c r="E60" s="38" t="inlineStr">
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="L60" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M60" s="38" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="96" customHeight="1">
+    <row r="61" ht="111" customHeight="1">
       <c r="A61" s="38" t="inlineStr">
         <is>
           <t>C-057</t>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D61" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.5”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais ao esgotamento sanitário nas comunidades”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
         </is>
       </c>
       <c r="E61" s="38" t="inlineStr">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="L61" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M61" s="38" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="96" customHeight="1">
+    <row r="62" ht="111" customHeight="1">
       <c r="A62" s="38" t="inlineStr">
         <is>
           <t>C-058</t>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="D62" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.5”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais ao esgotamento sanitário nas comunidades”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
         </is>
       </c>
       <c r="E62" s="38" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="L62" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M62" s="38" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="L63" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M63" s="38" t="n"/>
     </row>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="L64" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M64" s="38" t="n"/>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="F65" s="38" t="inlineStr">
         <is>
-          <t>O Acordo de Empréstimo, item (j)(vii), pede a identificação das áreas rurais da Parte 3.2. Incluir o m…</t>
+          <t>O Acordo de Empréstimo, item (j)(vii) das definições, exige a identificação das áreas rurais da Parte…</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="L65" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M65" s="38" t="inlineStr">
         <is>
@@ -8045,11 +8045,11 @@
         </is>
       </c>
       <c r="L66" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M66" s="38" t="n"/>
     </row>
-    <row r="67" ht="81" customHeight="1">
+    <row r="67" ht="96" customHeight="1">
       <c r="A67" s="38" t="inlineStr">
         <is>
           <t>C-063</t>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="D67" s="38" t="inlineStr">
         <is>
-          <t>6. Metas, indicadores e comprovação › Quadro “Critérios de aceite e evidências da Ação 3.2.2.6”, linha “Projeto sanitário”</t>
+          <t>6. Metas, indicadores e comprovação › Quadro “Critérios de aceite e evidências do esgotamento sanitário em mananciais”, linha “Projeto sanitário”</t>
         </is>
       </c>
       <c r="E67" s="38" t="inlineStr">
@@ -8106,7 +8106,7 @@
         </is>
       </c>
       <c r="L67" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M67" s="38" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="96" customHeight="1">
+    <row r="68" ht="111" customHeight="1">
       <c r="A68" s="38" t="inlineStr">
         <is>
           <t>C-064</t>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="D68" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.6”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais ao esgotamento sanitário em mananciais”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
         </is>
       </c>
       <c r="E68" s="38" t="inlineStr">
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="L68" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M68" s="38" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="96" customHeight="1">
+    <row r="69" ht="111" customHeight="1">
       <c r="A69" s="38" t="inlineStr">
         <is>
           <t>C-065</t>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="D69" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.6”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais ao esgotamento sanitário em mananciais”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
         </is>
       </c>
       <c r="E69" s="38" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="F69" s="38" t="inlineStr">
         <is>
-          <t>Dimensionamento conforme a ABNT NBR 17076:2024; distância segura de nascentes e cursos d'água; verificação técnica (MGAS)</t>
+          <t>Dimensionamento conforme a ABNT NBR 17076:2024; distâncias mínimas de nascentes e cursos d'água; verificação técnica (MGAS)</t>
         </is>
       </c>
       <c r="G69" s="38" t="inlineStr">
@@ -8236,7 +8236,7 @@
         </is>
       </c>
       <c r="L69" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M69" s="38" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="L70" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M70" s="38" t="n"/>
     </row>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="F71" s="38" t="inlineStr">
         <is>
-          <t>A supervisora é um dos instrumentos de cumprimento das NAS nas obras: verifica, em campo, os requisitos ambientais, sociais e de saúde e segurança que as A…</t>
+          <t>A supervisora constitui instrumento de cumprimento das NAS nas obras, mediante verificação em campo dos requisitos ambientais, sociais e de saúde e seguran…</t>
         </is>
       </c>
       <c r="G71" s="38" t="inlineStr">
@@ -8362,11 +8362,11 @@
         </is>
       </c>
       <c r="L71" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M71" s="38" t="n"/>
     </row>
-    <row r="72" ht="96" customHeight="1">
+    <row r="72" ht="111" customHeight="1">
       <c r="A72" s="38" t="inlineStr">
         <is>
           <t>C-068</t>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="D72" s="38" t="inlineStr">
         <is>
-          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à Ação 3.2.2.7”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
+          <t>7. Gestão de riscos e impactos ambientais e sociais › Quadro “Aplicação das Normas Ambientais e Sociais à supervisão e gerenciamento das obras”, linha “NAS 1 – Avaliação e gestão de riscos”</t>
         </is>
       </c>
       <c r="E72" s="38" t="inlineStr">
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="L72" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M72" s="38" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="L73" s="39" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M73" s="38" t="n"/>
     </row>
